--- a/products.xlsx
+++ b/products.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\barcode_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{016A7956-D567-473B-AE60-95CF1A69FD79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27748103-37B0-4908-BC45-588E420606F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="18300" windowHeight="9735" xr2:uid="{FB08337E-30C0-44F2-980F-D75898FE545D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FB08337E-30C0-44F2-980F-D75898FE545D}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
@@ -20,9 +20,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>A4 Paper</t>
+  </si>
+  <si>
+    <t>Notebook</t>
+  </si>
+  <si>
+    <t>Pencil</t>
   </si>
   <si>
     <t>Eraser</t>
@@ -44,12 +50,6 @@
   </si>
   <si>
     <t>สันรูด 17 มิล</t>
-  </si>
-  <si>
-    <t>ดินสอสี</t>
-  </si>
-  <si>
-    <t>สมุด</t>
   </si>
 </sst>
 </file>
@@ -536,7 +536,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -912,7 +912,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1C88C30-C61C-46C2-8143-957812C2D312}">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.125" customWidth="1"/>
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C1">
         <v>12</v>
@@ -932,10 +932,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>13</v>
@@ -943,21 +943,21 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>15.75</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>15</v>
@@ -965,398 +965,13 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>17.350000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>18.350000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8">
-        <v>19.350000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9">
-        <v>20.350000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10">
-        <v>21.35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11">
-        <v>22.35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12">
-        <v>23.35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13">
-        <v>24.35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14">
-        <v>25.35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C15">
-        <v>26.35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>27.35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17">
-        <v>28.35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18">
-        <v>29.35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19">
-        <v>30.35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20">
-        <v>31.35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21">
-        <v>32.35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C22">
-        <v>33.35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23">
-        <v>34.35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>1</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24">
-        <v>35.35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25">
-        <v>36.35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26">
-        <v>37.35</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>9</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C27">
-        <v>38.35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C28">
-        <v>39.35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>1</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C29">
-        <v>40.35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C30">
-        <v>41.35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31">
-        <v>42.35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32">
-        <v>43.35</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>8</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C33">
-        <v>44.35</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>1</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C34">
-        <v>45.35</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>7</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35">
-        <v>46.35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36">
-        <v>47.35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>9</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C37">
-        <v>48.35</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>8</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38">
-        <v>49.35</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>1</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C39">
-        <v>50.35</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>7</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40">
-        <v>51.35</v>
       </c>
     </row>
   </sheetData>
